--- a/base/cluster3-e-parametrico.xlsx
+++ b/base/cluster3-e-parametrico.xlsx
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado 18/04/2026 07:57</t>
+          <t>Gerado 18/04/2026 08:26</t>
         </is>
       </c>
     </row>
